--- a/qgis/template_shapefile/value_map/strandings_value_mapping.xlsx
+++ b/qgis/template_shapefile/value_map/strandings_value_mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\3 - Research\2 - PhD\1 - Publications\Chapter 3 - small_stranding\supplemental\final\template_shapefile\value_map\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s0951644\Desktop\strandings_from_space\qgis\template_shapefile\value_map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA66809B-8000-412E-B565-F7C0779F8B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26988164-3F76-45A3-86CD-4B5E4BA618F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="satellite" sheetId="3" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="274">
   <si>
     <t>otb_bayes_bco</t>
   </si>
@@ -662,9 +662,6 @@
     <t>maui_dolphin</t>
   </si>
   <si>
-    <t>eastern_north_pacific_long-beaked_common_dolphin</t>
-  </si>
-  <si>
     <t>black_sea_common_dolphin</t>
   </si>
   <si>
@@ -863,25 +860,13 @@
     <t>4,3,2</t>
   </si>
   <si>
-    <t xml:space="preserve">4_band_3,2,1 </t>
-  </si>
-  <si>
-    <t>4_band_1,2,3</t>
-  </si>
-  <si>
-    <t>4_band_4,3,1</t>
-  </si>
-  <si>
-    <t>6_band_4,3,2</t>
-  </si>
-  <si>
-    <t>8_band_5,3,2</t>
-  </si>
-  <si>
     <t>5,3,2</t>
   </si>
   <si>
-    <t>8_band_6,4,3</t>
+    <t>pukusi_franciscana</t>
+  </si>
+  <si>
+    <t>eastern_pacific_long-beaked_common_dolphin</t>
   </si>
 </sst>
 </file>
@@ -1365,9 +1350,10 @@
     <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="18" builtinId="30" customBuiltin="1"/>
@@ -2299,18 +2285,18 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -2331,18 +2317,18 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -2907,7 +2893,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>272</v>
+        <v>100</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>100</v>
@@ -2916,7 +2902,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>273</v>
+        <v>101</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>101</v>
@@ -2924,31 +2910,31 @@
     </row>
     <row r="3" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>278</v>
+        <v>102</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>102</v>
@@ -3128,7 +3114,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:D149"/>
+  <dimension ref="A1:D150"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -3182,7 +3168,7 @@
       <c r="A6" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>143</v>
       </c>
       <c r="C6" s="1"/>
@@ -3192,7 +3178,7 @@
       <c r="A7" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C7" s="1"/>
@@ -3202,7 +3188,7 @@
       <c r="A8" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>145</v>
       </c>
       <c r="C8" s="1"/>
@@ -3212,7 +3198,7 @@
       <c r="A9" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>146</v>
       </c>
       <c r="C9" s="1"/>
@@ -3222,7 +3208,7 @@
       <c r="A10" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C10" s="1"/>
@@ -3232,7 +3218,7 @@
       <c r="A11" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>147</v>
       </c>
       <c r="C11" s="1"/>
@@ -3242,7 +3228,7 @@
       <c r="A12" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>148</v>
       </c>
       <c r="C12" s="1"/>
@@ -3252,7 +3238,7 @@
       <c r="A13" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>149</v>
       </c>
       <c r="C13" s="1"/>
@@ -3262,7 +3248,7 @@
       <c r="A14" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C14" s="1"/>
@@ -3272,7 +3258,7 @@
       <c r="A15" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>151</v>
       </c>
       <c r="C15" s="1"/>
@@ -3282,7 +3268,7 @@
       <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="1"/>
@@ -3292,7 +3278,7 @@
       <c r="A17" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="2" t="s">
         <v>152</v>
       </c>
       <c r="C17" s="1"/>
@@ -3302,7 +3288,7 @@
       <c r="A18" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="2" t="s">
         <v>153</v>
       </c>
       <c r="C18" s="1"/>
@@ -3312,7 +3298,7 @@
       <c r="A19" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C19" s="1"/>
@@ -3322,7 +3308,7 @@
       <c r="A20" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="2" t="s">
         <v>155</v>
       </c>
       <c r="C20" s="1"/>
@@ -3332,7 +3318,7 @@
       <c r="A21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C21" s="1"/>
@@ -3342,7 +3328,7 @@
       <c r="A22" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C22" s="1"/>
@@ -3352,7 +3338,7 @@
       <c r="A23" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="2" t="s">
         <v>157</v>
       </c>
       <c r="C23" s="1"/>
@@ -3362,7 +3348,7 @@
       <c r="A24" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C24" s="1"/>
@@ -3372,7 +3358,7 @@
       <c r="A25" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C25" s="1"/>
@@ -3382,7 +3368,7 @@
       <c r="A26" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="2" t="s">
         <v>159</v>
       </c>
       <c r="C26" s="1"/>
@@ -3392,7 +3378,7 @@
       <c r="A27" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C27" s="1"/>
@@ -3402,7 +3388,7 @@
       <c r="A28" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="2" t="s">
         <v>160</v>
       </c>
       <c r="C28" s="1"/>
@@ -3412,7 +3398,7 @@
       <c r="A29" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="2" t="s">
         <v>161</v>
       </c>
       <c r="C29" s="1"/>
@@ -3422,7 +3408,7 @@
       <c r="A30" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="2" t="s">
         <v>162</v>
       </c>
       <c r="C30" s="1"/>
@@ -3432,7 +3418,7 @@
       <c r="A31" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="2" t="s">
         <v>163</v>
       </c>
       <c r="C31" s="1"/>
@@ -3442,7 +3428,7 @@
       <c r="A32" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C32" s="1"/>
@@ -3452,7 +3438,7 @@
       <c r="A33" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="2" t="s">
         <v>164</v>
       </c>
       <c r="C33" s="1"/>
@@ -3462,7 +3448,7 @@
       <c r="A34" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="2" t="s">
         <v>165</v>
       </c>
       <c r="C34" s="1"/>
@@ -3472,7 +3458,7 @@
       <c r="A35" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="2" t="s">
         <v>166</v>
       </c>
       <c r="C35" s="1"/>
@@ -3482,7 +3468,7 @@
       <c r="A36" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C36" s="1"/>
@@ -3492,7 +3478,7 @@
       <c r="A37" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C37" s="1"/>
@@ -3502,7 +3488,7 @@
       <c r="A38" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C38" s="1"/>
@@ -3512,7 +3498,7 @@
       <c r="A39" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="2" t="s">
         <v>167</v>
       </c>
       <c r="C39" s="1"/>
@@ -3522,7 +3508,7 @@
       <c r="A40" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="2" t="s">
         <v>168</v>
       </c>
       <c r="C40" s="1"/>
@@ -3532,7 +3518,7 @@
       <c r="A41" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="2" t="s">
         <v>169</v>
       </c>
       <c r="C41" s="1"/>
@@ -3542,7 +3528,7 @@
       <c r="A42" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="2" t="s">
         <v>170</v>
       </c>
       <c r="C42" s="1"/>
@@ -3552,7 +3538,7 @@
       <c r="A43" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="2" t="s">
         <v>171</v>
       </c>
       <c r="C43" s="1"/>
@@ -3562,7 +3548,7 @@
       <c r="A44" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C44" s="1"/>
@@ -3572,7 +3558,7 @@
       <c r="A45" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="2" t="s">
         <v>172</v>
       </c>
       <c r="C45" s="1"/>
@@ -3582,7 +3568,7 @@
       <c r="A46" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C46" s="1"/>
@@ -3592,7 +3578,7 @@
       <c r="A47" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C47" s="1"/>
@@ -3602,7 +3588,7 @@
       <c r="A48" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="2" t="s">
         <v>175</v>
       </c>
       <c r="C48" s="1"/>
@@ -3612,7 +3598,7 @@
       <c r="A49" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C49" s="1"/>
@@ -3622,7 +3608,7 @@
       <c r="A50" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C50" s="1"/>
@@ -3632,7 +3618,7 @@
       <c r="A51" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="2" t="s">
         <v>178</v>
       </c>
       <c r="C51" s="1"/>
@@ -3640,10 +3626,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>260</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -3652,7 +3638,7 @@
       <c r="A53" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="2" t="s">
         <v>179</v>
       </c>
       <c r="C53" s="1"/>
@@ -3662,7 +3648,7 @@
       <c r="A54" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="2" t="s">
         <v>180</v>
       </c>
       <c r="C54" s="1"/>
@@ -3672,7 +3658,7 @@
       <c r="A55" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="2" t="s">
         <v>181</v>
       </c>
       <c r="C55" s="1"/>
@@ -3682,7 +3668,7 @@
       <c r="A56" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="2" t="s">
         <v>182</v>
       </c>
       <c r="C56" s="1"/>
@@ -3692,7 +3678,7 @@
       <c r="A57" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="2" t="s">
         <v>183</v>
       </c>
       <c r="C57" s="1"/>
@@ -3702,7 +3688,7 @@
       <c r="A58" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C58" s="1"/>
@@ -3712,7 +3698,7 @@
       <c r="A59" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="2" t="s">
         <v>185</v>
       </c>
       <c r="C59" s="1"/>
@@ -3722,7 +3708,7 @@
       <c r="A60" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C60" s="1"/>
@@ -3732,7 +3718,7 @@
       <c r="A61" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="2" t="s">
         <v>187</v>
       </c>
       <c r="C61" s="1"/>
@@ -3742,7 +3728,7 @@
       <c r="A62" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="2" t="s">
         <v>188</v>
       </c>
       <c r="C62" s="1"/>
@@ -3752,7 +3738,7 @@
       <c r="A63" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="2" t="s">
         <v>189</v>
       </c>
       <c r="C63" s="1"/>
@@ -3762,7 +3748,7 @@
       <c r="A64" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="2" t="s">
         <v>190</v>
       </c>
       <c r="C64" s="1"/>
@@ -3772,7 +3758,7 @@
       <c r="A65" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="2" t="s">
         <v>191</v>
       </c>
       <c r="C65" s="1"/>
@@ -3782,7 +3768,7 @@
       <c r="A66" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="2" t="s">
         <v>192</v>
       </c>
       <c r="C66" s="1"/>
@@ -3792,7 +3778,7 @@
       <c r="A67" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="2" t="s">
         <v>193</v>
       </c>
       <c r="C67" s="1"/>
@@ -3802,7 +3788,7 @@
       <c r="A68" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C68" s="1"/>
@@ -3810,10 +3796,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>261</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
@@ -3822,692 +3808,700 @@
       <c r="A70" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="2" t="s">
         <v>195</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
+        <v>272</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>196</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>197</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>198</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>199</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>200</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>201</v>
       </c>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>202</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>203</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>31</v>
+        <v>204</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>204</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>205</v>
+        <v>31</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>206</v>
+        <v>273</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>205</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>36</v>
+        <v>206</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>206</v>
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>208</v>
+        <v>38</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>208</v>
       </c>
       <c r="C89" s="1"/>
       <c r="D89" s="1"/>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>209</v>
       </c>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>210</v>
       </c>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>211</v>
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>212</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>213</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>214</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>32</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C96" s="1"/>
+      <c r="D96" s="1"/>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>217</v>
+        <v>32</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>28</v>
+        <v>222</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>263</v>
+        <v>28</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>37</v>
+        <v>264</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>224</v>
+        <v>35</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>30</v>
+        <v>234</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>236</v>
+        <v>30</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>34</v>
+        <v>240</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>242</v>
+        <v>34</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>266</v>
+        <v>241</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>244</v>
+        <v>265</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>267</v>
+        <v>244</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>243</v>
+        <v>266</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>43</v>
+        <v>248</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>250</v>
+        <v>43</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A150" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>257</v>
       </c>
     </row>
   </sheetData>
